--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N109_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N109_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.41344582477569</v>
+        <v>5.42968494652605</v>
       </c>
       <c r="D2" t="n">
-        <v>32.59707078805526</v>
+        <v>5.297024003058979</v>
       </c>
       <c r="E2" t="n">
-        <v>10.47399103206696</v>
+        <v>1.702023542710882</v>
       </c>
       <c r="F2" t="n">
-        <v>11.19381627101889</v>
+        <v>1.818995144040569</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.36118815365859</v>
+        <v>5.908693074969521</v>
       </c>
       <c r="D3" t="n">
-        <v>37.22588761729489</v>
+        <v>6.04920673781042</v>
       </c>
       <c r="E3" t="n">
-        <v>10.47399103206696</v>
+        <v>1.702023542710882</v>
       </c>
       <c r="F3" t="n">
-        <v>11.19381627101889</v>
+        <v>1.818995144040569</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.15343012548156</v>
+        <v>7.987432395390753</v>
       </c>
       <c r="D4" t="n">
-        <v>48.54687475833295</v>
+        <v>7.888867148229106</v>
       </c>
       <c r="E4" t="n">
-        <v>10.47399103206696</v>
+        <v>1.702023542710882</v>
       </c>
       <c r="F4" t="n">
-        <v>11.19381627101889</v>
+        <v>1.818995144040569</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.00399461662179</v>
+        <v>3.413149125201041</v>
       </c>
       <c r="D5" t="n">
-        <v>19.2675514228046</v>
+        <v>3.130977106205748</v>
       </c>
       <c r="E5" t="n">
-        <v>10.47399103206696</v>
+        <v>1.702023542710882</v>
       </c>
       <c r="F5" t="n">
-        <v>11.19381627101889</v>
+        <v>1.818995144040569</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.21812333885453</v>
+        <v>4.097945042563861</v>
       </c>
       <c r="D6" t="n">
-        <v>17.96997704907474</v>
+        <v>2.920121270474644</v>
       </c>
       <c r="E6" t="n">
-        <v>10.47399103206696</v>
+        <v>1.702023542710882</v>
       </c>
       <c r="F6" t="n">
-        <v>11.19381627101889</v>
+        <v>1.818995144040569</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>48.3886759248423</v>
+        <v>7.863159837786875</v>
       </c>
       <c r="D7" t="n">
-        <v>50.10646827771147</v>
+        <v>8.142301095128115</v>
       </c>
       <c r="E7" t="n">
-        <v>10.47399103206696</v>
+        <v>1.702023542710882</v>
       </c>
       <c r="F7" t="n">
-        <v>11.19381627101889</v>
+        <v>1.818995144040569</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.04439120335512</v>
+        <v>5.532213570545207</v>
       </c>
       <c r="D8" t="n">
-        <v>34.08336975054758</v>
+        <v>5.538547584463982</v>
       </c>
       <c r="E8" t="n">
-        <v>10.47399103206696</v>
+        <v>1.702023542710882</v>
       </c>
       <c r="F8" t="n">
-        <v>11.19381627101889</v>
+        <v>1.818995144040569</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.28433486972875</v>
+        <v>3.783704416330922</v>
       </c>
       <c r="D9" t="n">
-        <v>23.20834885608308</v>
+        <v>3.771356689113501</v>
       </c>
       <c r="E9" t="n">
-        <v>10.47399103206696</v>
+        <v>1.702023542710882</v>
       </c>
       <c r="F9" t="n">
-        <v>11.19381627101889</v>
+        <v>1.818995144040569</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>14.95539140978319</v>
+        <v>2.430251104089769</v>
       </c>
       <c r="D10" t="n">
-        <v>17.05049747252546</v>
+        <v>2.770705839285388</v>
       </c>
       <c r="E10" t="n">
-        <v>10.47399103206696</v>
+        <v>1.702023542710882</v>
       </c>
       <c r="F10" t="n">
-        <v>11.19381627101889</v>
+        <v>1.818995144040569</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>36.43455918071953</v>
+        <v>5.920615866866924</v>
       </c>
       <c r="D11" t="n">
-        <v>28.92141228563903</v>
+        <v>4.699729496416343</v>
       </c>
       <c r="E11" t="n">
-        <v>10.47399103206696</v>
+        <v>1.702023542710882</v>
       </c>
       <c r="F11" t="n">
-        <v>11.19381627101889</v>
+        <v>1.818995144040569</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>24.49705511635826</v>
+        <v>3.980771456408218</v>
       </c>
       <c r="D12" t="n">
-        <v>22.92946915098477</v>
+        <v>3.726038737035025</v>
       </c>
       <c r="E12" t="n">
-        <v>10.47399103206696</v>
+        <v>1.702023542710882</v>
       </c>
       <c r="F12" t="n">
-        <v>11.19381627101889</v>
+        <v>1.818995144040569</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>16.04021602138064</v>
+        <v>2.606535103474354</v>
       </c>
       <c r="D13" t="n">
-        <v>19.68742418910646</v>
+        <v>3.1992064307298</v>
       </c>
       <c r="E13" t="n">
-        <v>10.47399103206696</v>
+        <v>1.702023542710882</v>
       </c>
       <c r="F13" t="n">
-        <v>11.19381627101889</v>
+        <v>1.818995144040569</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>18.85750104833036</v>
+        <v>3.064343920353684</v>
       </c>
       <c r="D14" t="n">
-        <v>11.5686629934513</v>
+        <v>1.879907736435836</v>
       </c>
       <c r="E14" t="n">
-        <v>10.47399103206696</v>
+        <v>1.702023542710882</v>
       </c>
       <c r="F14" t="n">
-        <v>11.19381627101889</v>
+        <v>1.818995144040569</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>27.96529091142297</v>
+        <v>4.544359773106232</v>
       </c>
       <c r="D15" t="n">
-        <v>23.94437199475777</v>
+        <v>3.890960449148137</v>
       </c>
       <c r="E15" t="n">
-        <v>10.47399103206696</v>
+        <v>1.702023542710882</v>
       </c>
       <c r="F15" t="n">
-        <v>11.19381627101889</v>
+        <v>1.818995144040569</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
